--- a/config.xlsx
+++ b/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F404A59-0AD6-4B09-B541-B17FBDA43CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA91F3D-FFAB-437F-98CA-C3C6AA280F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>smartcards.xlsx</t>
+    <t>vocabolario.xlsx</t>
   </si>
   <si>
-    <t>Test_mitSP</t>
-  </si>
-  <si>
-    <t>Test_ohneSP</t>
-  </si>
-  <si>
-    <t>smartcards_ohneSP.xlsx</t>
+    <t>VocabolarIo A1-A2</t>
   </si>
 </sst>
 </file>
@@ -383,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -406,14 +400,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config.xlsx
+++ b/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA91F3D-FFAB-437F-98CA-C3C6AA280F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F404A59-0AD6-4B09-B541-B17FBDA43CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -28,10 +28,16 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>vocabolario.xlsx</t>
-  </si>
-  <si>
-    <t>VocabolarIo A1-A2</t>
+    <t>smartcards.xlsx</t>
+  </si>
+  <si>
+    <t>Test_mitSP</t>
+  </si>
+  <si>
+    <t>Test_ohneSP</t>
+  </si>
+  <si>
+    <t>smartcards_ohneSP.xlsx</t>
   </si>
 </sst>
 </file>
@@ -377,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -400,6 +406,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config.xlsx
+++ b/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F404A59-0AD6-4B09-B541-B17FBDA43CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B2E5A6-3F12-451B-B0A6-0DC97C18FECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="696" yWindow="2508" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>smartcards_ohneSP.xlsx</t>
+  </si>
+  <si>
+    <t>1x1</t>
+  </si>
+  <si>
+    <t>SmartCards_Einmaleins.xlsx</t>
   </si>
 </sst>
 </file>
@@ -383,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -414,6 +420,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B2E5A6-3F12-451B-B0A6-0DC97C18FECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF76405-D4F4-407B-B01D-56AF68375B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="2508" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>SmartCards_Einmaleins.xlsx</t>
+  </si>
+  <si>
+    <t>Test_Prüffeld</t>
+  </si>
+  <si>
+    <t>smartcards_muster_mit.xlsx</t>
   </si>
 </sst>
 </file>
@@ -389,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -428,6 +434,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF76405-D4F4-407B-B01D-56AF68375B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1F0664-F925-4EBD-9B27-3D9CDA1248F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -28,28 +28,16 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>smartcards.xlsx</t>
-  </si>
-  <si>
-    <t>Test_mitSP</t>
-  </si>
-  <si>
-    <t>Test_ohneSP</t>
-  </si>
-  <si>
-    <t>smartcards_ohneSP.xlsx</t>
-  </si>
-  <si>
     <t>1x1</t>
   </si>
   <si>
-    <t>SmartCards_Einmaleins.xlsx</t>
-  </si>
-  <si>
-    <t>Test_Prüffeld</t>
-  </si>
-  <si>
-    <t>smartcards_muster_mit.xlsx</t>
+    <t>Test Decks</t>
+  </si>
+  <si>
+    <t>smartcards_Testdecks.xlsx</t>
+  </si>
+  <si>
+    <t>smartcards_1x1.xlsx</t>
   </si>
 </sst>
 </file>
@@ -395,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -415,31 +403,15 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
